--- a/AlarmProcessor/monitoring.xlsx
+++ b/AlarmProcessor/monitoring.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10111"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10611"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/whuaning/Git/AutoOps/AlarmProcessor/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4218DBD3-0AFA-0945-9C81-7BB1F902F7AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23BAB6E1-C395-9A45-A7C7-91584E01B688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="500" windowWidth="27620" windowHeight="17040" activeTab="1" xr2:uid="{EFA5CA1F-2FCE-F944-B84C-F49CCED66540}"/>
+    <workbookView xWindow="1080" yWindow="500" windowWidth="27620" windowHeight="16180" xr2:uid="{EFA5CA1F-2FCE-F944-B84C-F49CCED66540}"/>
   </bookViews>
   <sheets>
     <sheet name="指标告警清单" sheetId="1" r:id="rId1"/>
@@ -24,9 +24,10 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="322">
   <si>
     <t>考虑将更大的实例类型用于您的专用主节点。由于其在集群稳定性和蓝/绿部署中的作用，专用主节点的 CPU 使用率应比数据节点低。</t>
   </si>
@@ -285,18 +286,12 @@
     <t>ReadLatency</t>
   </si>
   <si>
-    <t>ReadThroughput</t>
-  </si>
-  <si>
     <t>ReplicaLag</t>
   </si>
   <si>
     <t>WriteLatency</t>
   </si>
   <si>
-    <t>WriteThroughput</t>
-  </si>
-  <si>
     <t>EngineCPUUtilization</t>
   </si>
   <si>
@@ -309,22 +304,10 @@
     <t>此指标不应超过 50 MB。</t>
   </si>
   <si>
-    <t>Evictions</t>
-  </si>
-  <si>
-    <t>CurrConnections</t>
-  </si>
-  <si>
     <t>DatabaseMemoryUsagePercentage</t>
   </si>
   <si>
     <t>&gt;=75</t>
-  </si>
-  <si>
-    <t>NewConnections</t>
-  </si>
-  <si>
-    <t>&gt;=60000</t>
   </si>
   <si>
     <t>ReplicationLag</t>
@@ -412,9 +395,6 @@
     <t>HTTPCode_Target_5XX_Count/RequestCount</t>
   </si>
   <si>
-    <t>MemoryFree/(MemoryFree+MemoryUsed)</t>
-  </si>
-  <si>
     <t>后端服务器健康检查失败</t>
   </si>
   <si>
@@ -469,19 +449,7 @@
     <t>ReadIOPS+WriteIOPS</t>
   </si>
   <si>
-    <t>内存不足导致缓存内容被驱离</t>
-  </si>
-  <si>
-    <t>每个节点有65000并发连接上限的硬限制，根据连接情况设定60000以下的阈值</t>
-  </si>
-  <si>
-    <t>磁盘不足</t>
-  </si>
-  <si>
     <t>NetworkRxDropped/NetworkRxPackets</t>
-  </si>
-  <si>
-    <t>NetworkTxDropped/NetworkTxDropped</t>
   </si>
   <si>
     <t>根据预置IOPS设定阈值</t>
@@ -935,13 +903,119 @@
   </si>
   <si>
     <t>安全组已修改。</t>
+  </si>
+  <si>
+    <t>MaxOffsetLag</t>
+  </si>
+  <si>
+    <t>EstimatedMaxTimeLag</t>
+  </si>
+  <si>
+    <t>MSK Topic/Consumer Group</t>
+  </si>
+  <si>
+    <t>堆积消息消费时延大</t>
+  </si>
+  <si>
+    <t>堆积消息预计消费时延</t>
+  </si>
+  <si>
+    <t>要避免出现因磁盘空间不足而无法保存消息的情况，您可以创建一个 CloudWatch 警报器监视KafkaDataLogsDiskUsed指标。当此指标的值达到或超过 85% 时，请执行下列一项或多项操作：
+1.使用自动扩展。您也可以手动增加代理存储空间，如中所述手动扩展.
+2.缩短消息保留期或减小日志大小。有关如何做到这一点的信息，请参阅调整数据保留参数。
+3.删除未使用的主题。</t>
+  </si>
+  <si>
+    <t>HeapMemoryAfterGC</t>
+  </si>
+  <si>
+    <t>要确定 Apache Kafka 使用了多少内存，您可以监视HeapMemoryAfterGC指标。HeapMemoryAfterGC是垃圾回收后使用中的总堆内存的百分比。建议您创建一个 CloudWatch 警报在以下情况下采取行动HeapMemoryAfterGC增加到 60% 以上。
+您可以执行的减少内存使用率的步骤各不相同。它们取决于你配置 Apache Kafka 的方式。例如，如果您使用事务性消息传递，则可以减少transactional.id.expiration.ms你的 Apache Kafka 配置中的值来自604800000ms 到86400000毫秒（从 7 天到 1 天）。这减少了每个事务的内存占用。</t>
+  </si>
+  <si>
+    <t>CPUCreditBalance</t>
+  </si>
+  <si>
+    <t>&lt;=60</t>
+  </si>
+  <si>
+    <t>实例自启动后已累积获得的 CPU 积分数</t>
+  </si>
+  <si>
+    <t>EBS卷</t>
+  </si>
+  <si>
+    <t>AWS/EBS</t>
+  </si>
+  <si>
+    <t>(VolumeWriteOps+VolumeReadOps)/IF(PERIOD(VolumeIdleTime)-m3&gt;1, PERIOD(VolumeIdleTime)-m3, 1)</t>
+  </si>
+  <si>
+    <t>粒度时间内的IOPS峰值</t>
+  </si>
+  <si>
+    <t>(VolumeWriteBytes+VolumeReadBytes)/IF(PERIOD(VolumeIdleTime)-m3&gt;1, PERIOD(VolumeIdleTime)-m3, 1)</t>
+  </si>
+  <si>
+    <t>粒度时间内的I吞吐量峰值</t>
+  </si>
+  <si>
+    <t>ReadThroughput+WriteThroughput</t>
+  </si>
+  <si>
+    <t>根据预置吞吐量设定阈值</t>
+  </si>
+  <si>
+    <t>VPN连接</t>
+  </si>
+  <si>
+    <t>AWS/VPN</t>
+  </si>
+  <si>
+    <t>TunnelState</t>
+  </si>
+  <si>
+    <t>&lt;=1</t>
+  </si>
+  <si>
+    <t>1表示连接总的两个隧道都健康，0.5表示只有一个隧道健康，0表示两个隧道的已经中断</t>
+  </si>
+  <si>
+    <t>TunnelDataOut</t>
+  </si>
+  <si>
+    <t>TunnelDataIn</t>
+  </si>
+  <si>
+    <t>NetworkBandwidthInAllowanceExceeded</t>
+  </si>
+  <si>
+    <t>由于网络带宽限制导致丢包数目</t>
+  </si>
+  <si>
+    <t>NetworkBandwidthOutAllowanceExceeded</t>
+  </si>
+  <si>
+    <t>NetworkConntrackAllowanceExceeded</t>
+  </si>
+  <si>
+    <t>由于安全组链接跟踪数量限制导致丢包数目</t>
+  </si>
+  <si>
+    <t>NetworkPacketsPerSecondAllowanceExceeded</t>
+  </si>
+  <si>
+    <t>由于网络PPS限制导致丢包数目</t>
+  </si>
+  <si>
+    <t>NetworkTxDropped/NetworkTxPackets</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -971,6 +1045,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -980,7 +1061,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -988,12 +1069,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1001,6 +1097,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1325,10 +1425,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{157529DC-4008-E74A-89F0-DDFA0B3936F3}">
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21.1640625" bestFit="1" customWidth="1"/>
@@ -1337,14 +1437,14 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
+        <v>148</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
     </row>
     <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
@@ -1366,7 +1466,7 @@
         <v>5</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="17" x14ac:dyDescent="0.2">
@@ -1400,19 +1500,19 @@
         <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>161</v>
+        <v>296</v>
       </c>
       <c r="D4">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>8</v>
+        <v>297</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>38</v>
+        <v>298</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="17" x14ac:dyDescent="0.2">
@@ -1423,45 +1523,45 @@
         <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>150</v>
       </c>
       <c r="D5">
         <v>60</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" t="s">
         <v>8</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="17" hidden="1" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>51</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D6">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="E6">
         <v>3</v>
       </c>
       <c r="F6" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="17" hidden="1" x14ac:dyDescent="0.2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>51</v>
       </c>
@@ -1469,22 +1569,22 @@
         <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D7">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="17" hidden="1" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>51</v>
       </c>
@@ -1492,7 +1592,7 @@
         <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D8">
         <v>60</v>
@@ -1501,13 +1601,13 @@
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="17" hidden="1" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -1515,22 +1615,22 @@
         <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="D9">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="17" hidden="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>51</v>
       </c>
@@ -1538,7 +1638,7 @@
         <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D10">
         <v>300</v>
@@ -1553,7 +1653,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="17" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>51</v>
       </c>
@@ -1561,22 +1661,22 @@
         <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>128</v>
+        <v>75</v>
       </c>
       <c r="D11">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>130</v>
+        <v>64</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="17" hidden="1" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>51</v>
       </c>
@@ -1584,7 +1684,7 @@
         <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="D12">
         <v>60</v>
@@ -1593,13 +1693,13 @@
         <v>3</v>
       </c>
       <c r="F12" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="17" hidden="1" x14ac:dyDescent="0.2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>51</v>
       </c>
@@ -1607,79 +1707,70 @@
         <v>40</v>
       </c>
       <c r="C13" t="s">
-        <v>76</v>
+        <v>122</v>
       </c>
       <c r="D13">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F13" t="s">
-        <v>64</v>
+        <v>123</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B14" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="D14">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>8</v>
+        <v>64</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>52</v>
+        <v>299</v>
       </c>
       <c r="B15" t="s">
-        <v>48</v>
+        <v>300</v>
       </c>
       <c r="C15" t="s">
-        <v>59</v>
-      </c>
-      <c r="D15">
-        <v>300</v>
-      </c>
-      <c r="E15">
-        <v>1</v>
-      </c>
-      <c r="F15" t="s">
-        <v>64</v>
+        <v>301</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>156</v>
+        <v>302</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>52</v>
+        <v>299</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
+        <v>300</v>
       </c>
       <c r="C16" t="s">
-        <v>58</v>
+        <v>303</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>133</v>
+        <v>304</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="17" x14ac:dyDescent="0.2">
@@ -1690,10 +1781,19 @@
         <v>48</v>
       </c>
       <c r="C17" t="s">
-        <v>65</v>
+        <v>47</v>
+      </c>
+      <c r="D17">
+        <v>60</v>
+      </c>
+      <c r="E17">
+        <v>3</v>
+      </c>
+      <c r="F17" t="s">
+        <v>8</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="17" x14ac:dyDescent="0.2">
@@ -1704,10 +1804,19 @@
         <v>48</v>
       </c>
       <c r="C18" t="s">
-        <v>66</v>
+        <v>59</v>
+      </c>
+      <c r="D18">
+        <v>300</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18" t="s">
+        <v>64</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="17" x14ac:dyDescent="0.2">
@@ -1718,10 +1827,10 @@
         <v>48</v>
       </c>
       <c r="C19" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="17" x14ac:dyDescent="0.2">
@@ -1732,10 +1841,10 @@
         <v>48</v>
       </c>
       <c r="C20" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="17" x14ac:dyDescent="0.2">
@@ -1746,13 +1855,13 @@
         <v>48</v>
       </c>
       <c r="C21" t="s">
-        <v>150</v>
+        <v>66</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="68" x14ac:dyDescent="0.2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>52</v>
       </c>
@@ -1760,68 +1869,59 @@
         <v>48</v>
       </c>
       <c r="C22" t="s">
-        <v>124</v>
-      </c>
-      <c r="D22">
-        <v>60</v>
-      </c>
-      <c r="E22">
-        <v>3</v>
-      </c>
-      <c r="F22" s="4"/>
+        <v>67</v>
+      </c>
       <c r="G22" s="1" t="s">
-        <v>162</v>
+        <v>128</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C23" t="s">
-        <v>47</v>
-      </c>
-      <c r="D23">
-        <v>60</v>
-      </c>
-      <c r="E23">
-        <v>3</v>
-      </c>
-      <c r="F23" t="s">
-        <v>8</v>
+        <v>68</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C24" t="s">
-        <v>69</v>
+        <v>139</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C25" t="s">
-        <v>70</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="D25">
+        <v>60</v>
+      </c>
+      <c r="E25">
+        <v>3</v>
+      </c>
+      <c r="F25" s="4"/>
       <c r="G25" s="1" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="17" x14ac:dyDescent="0.2">
@@ -1832,10 +1932,19 @@
         <v>49</v>
       </c>
       <c r="C26" t="s">
-        <v>71</v>
+        <v>47</v>
+      </c>
+      <c r="D26">
+        <v>60</v>
+      </c>
+      <c r="E26">
+        <v>3</v>
+      </c>
+      <c r="F26" t="s">
+        <v>8</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>138</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="17" x14ac:dyDescent="0.2">
@@ -1846,10 +1955,10 @@
         <v>49</v>
       </c>
       <c r="C27" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="17" x14ac:dyDescent="0.2">
@@ -1860,10 +1969,10 @@
         <v>49</v>
       </c>
       <c r="C28" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="17" x14ac:dyDescent="0.2">
@@ -1874,70 +1983,52 @@
         <v>49</v>
       </c>
       <c r="C29" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B30" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C30" t="s">
-        <v>16</v>
-      </c>
-      <c r="D30">
-        <v>300</v>
-      </c>
-      <c r="E30">
-        <v>3</v>
-      </c>
-      <c r="F30" t="s">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>62</v>
+        <v>132</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B31" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C31" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B32" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C32" t="s">
-        <v>80</v>
-      </c>
-      <c r="D32">
-        <v>300</v>
-      </c>
-      <c r="E32">
-        <v>1</v>
-      </c>
-      <c r="F32" t="s">
-        <v>22</v>
+        <v>73</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>81</v>
+        <v>133</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="17" x14ac:dyDescent="0.2">
@@ -1948,10 +2039,19 @@
         <v>46</v>
       </c>
       <c r="C33" t="s">
-        <v>78</v>
+        <v>16</v>
+      </c>
+      <c r="D33">
+        <v>300</v>
+      </c>
+      <c r="E33">
+        <v>3</v>
+      </c>
+      <c r="F33" t="s">
+        <v>18</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>142</v>
+        <v>62</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="17" x14ac:dyDescent="0.2">
@@ -1962,19 +2062,10 @@
         <v>46</v>
       </c>
       <c r="C34" t="s">
-        <v>10</v>
-      </c>
-      <c r="D34">
-        <v>60</v>
-      </c>
-      <c r="E34">
-        <v>1</v>
-      </c>
-      <c r="F34" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>79</v>
+        <v>134</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="17" x14ac:dyDescent="0.2">
@@ -1985,19 +2076,19 @@
         <v>46</v>
       </c>
       <c r="C35" t="s">
-        <v>143</v>
+        <v>80</v>
       </c>
       <c r="D35">
         <v>300</v>
       </c>
       <c r="E35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F35" t="s">
-        <v>149</v>
+        <v>22</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="17" x14ac:dyDescent="0.2">
@@ -2008,19 +2099,10 @@
         <v>46</v>
       </c>
       <c r="C36" t="s">
-        <v>82</v>
-      </c>
-      <c r="D36">
-        <v>300</v>
-      </c>
-      <c r="E36">
-        <v>1</v>
-      </c>
-      <c r="F36" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>63</v>
+        <v>135</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="17" x14ac:dyDescent="0.2">
@@ -2031,10 +2113,19 @@
         <v>46</v>
       </c>
       <c r="C37" t="s">
-        <v>83</v>
+        <v>10</v>
+      </c>
+      <c r="D37">
+        <v>60</v>
+      </c>
+      <c r="E37">
+        <v>1</v>
+      </c>
+      <c r="F37" t="s">
+        <v>11</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>140</v>
+        <v>79</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="17" x14ac:dyDescent="0.2">
@@ -2045,16 +2136,16 @@
         <v>46</v>
       </c>
       <c r="C38" t="s">
-        <v>84</v>
+        <v>136</v>
       </c>
       <c r="D38">
         <v>300</v>
       </c>
       <c r="E38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F38" t="s">
-        <v>64</v>
+        <v>138</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>63</v>
@@ -2068,7 +2159,7 @@
         <v>46</v>
       </c>
       <c r="C39" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D39">
         <v>300</v>
@@ -2091,264 +2182,283 @@
         <v>46</v>
       </c>
       <c r="C40" t="s">
-        <v>86</v>
+        <v>305</v>
+      </c>
+      <c r="D40">
+        <v>300</v>
+      </c>
+      <c r="E40">
+        <v>3</v>
+      </c>
+      <c r="F40" t="s">
+        <v>306</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="119" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="B41" t="s">
-        <v>101</v>
+        <v>46</v>
       </c>
       <c r="C41" t="s">
-        <v>16</v>
+        <v>83</v>
       </c>
       <c r="D41">
         <v>300</v>
       </c>
       <c r="E41">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F41" t="s">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="68" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="B42" t="s">
-        <v>101</v>
+        <v>46</v>
       </c>
       <c r="C42" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D42">
         <v>300</v>
       </c>
       <c r="E42">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="119" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B43" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="C43" t="s">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="D43">
         <v>300</v>
       </c>
       <c r="E43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F43" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B44" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="C44" t="s">
-        <v>91</v>
+        <v>85</v>
+      </c>
+      <c r="D44">
+        <v>300</v>
+      </c>
+      <c r="E44">
+        <v>3</v>
+      </c>
+      <c r="F44" t="s">
+        <v>18</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B45" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="C45" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D45">
         <v>300</v>
       </c>
       <c r="E45">
+        <v>1</v>
+      </c>
+      <c r="F45" t="s">
+        <v>22</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A46" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="D46" s="6">
+        <v>300</v>
+      </c>
+      <c r="E46" s="6">
         <v>3</v>
       </c>
-      <c r="F45" t="s">
+      <c r="F46" s="6"/>
+      <c r="G46" s="6" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A47" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="G45" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>102</v>
-      </c>
-      <c r="B46" t="s">
-        <v>101</v>
-      </c>
-      <c r="C46" t="s">
+      <c r="B47" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="G46" s="1" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>102</v>
-      </c>
-      <c r="B47" t="s">
-        <v>101</v>
-      </c>
-      <c r="C47" t="s">
-        <v>93</v>
-      </c>
-      <c r="D47">
+      <c r="C47" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D47" s="6">
         <v>300</v>
       </c>
-      <c r="E47">
+      <c r="E47" s="6">
         <v>3</v>
       </c>
-      <c r="F47" t="s">
-        <v>94</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
-        <v>102</v>
-      </c>
-      <c r="B48" t="s">
-        <v>101</v>
-      </c>
-      <c r="C48" t="s">
-        <v>99</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>102</v>
-      </c>
-      <c r="B49" t="s">
-        <v>101</v>
-      </c>
-      <c r="C49" t="s">
-        <v>97</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>63</v>
+      <c r="F47" s="6"/>
+      <c r="G47" s="6" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A48" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="D48" s="6">
+        <v>300</v>
+      </c>
+      <c r="E48" s="6">
+        <v>3</v>
+      </c>
+      <c r="F48" s="6"/>
+      <c r="G48" s="6" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A49" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="D49" s="6">
+        <v>300</v>
+      </c>
+      <c r="E49" s="6">
+        <v>3</v>
+      </c>
+      <c r="F49" s="6"/>
+      <c r="G49" s="6" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B50" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="C50" t="s">
-        <v>98</v>
+        <v>89</v>
+      </c>
+      <c r="D50">
+        <v>300</v>
+      </c>
+      <c r="E50">
+        <v>3</v>
+      </c>
+      <c r="F50" t="s">
+        <v>90</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>63</v>
+        <v>94</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="B51" t="s">
-        <v>7</v>
+        <v>95</v>
       </c>
       <c r="C51" t="s">
-        <v>6</v>
-      </c>
-      <c r="D51">
-        <v>60</v>
-      </c>
-      <c r="E51">
-        <v>1</v>
-      </c>
-      <c r="F51" t="s">
-        <v>8</v>
+        <v>93</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="B52" t="s">
-        <v>7</v>
+        <v>95</v>
       </c>
       <c r="C52" t="s">
-        <v>9</v>
-      </c>
-      <c r="D52">
-        <v>60</v>
-      </c>
-      <c r="E52">
-        <v>1</v>
-      </c>
-      <c r="F52" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="68" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="B53" t="s">
-        <v>7</v>
+        <v>95</v>
       </c>
       <c r="C53" t="s">
-        <v>10</v>
-      </c>
-      <c r="D53">
-        <v>60</v>
-      </c>
-      <c r="E53">
-        <v>1</v>
-      </c>
-      <c r="F53" t="s">
-        <v>11</v>
+        <v>92</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="17" x14ac:dyDescent="0.2">
@@ -2359,10 +2469,10 @@
         <v>7</v>
       </c>
       <c r="C54" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D54">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="E54">
         <v>1</v>
@@ -2371,10 +2481,10 @@
         <v>8</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="51" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>54</v>
       </c>
@@ -2382,22 +2492,22 @@
         <v>7</v>
       </c>
       <c r="C55" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D55">
-        <v>900</v>
+        <v>60</v>
       </c>
       <c r="E55">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F55" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>54</v>
       </c>
@@ -2405,7 +2515,7 @@
         <v>7</v>
       </c>
       <c r="C56" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D56">
         <v>60</v>
@@ -2414,13 +2524,13 @@
         <v>1</v>
       </c>
       <c r="F56" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>54</v>
       </c>
@@ -2428,22 +2538,22 @@
         <v>7</v>
       </c>
       <c r="C57" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D57">
         <v>300</v>
       </c>
       <c r="E57">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F57" t="s">
-        <v>18</v>
-      </c>
-      <c r="G57" s="6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+        <v>8</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>54</v>
       </c>
@@ -2451,20 +2561,22 @@
         <v>7</v>
       </c>
       <c r="C58" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D58">
-        <v>300</v>
+        <v>900</v>
       </c>
       <c r="E58">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F58" t="s">
-        <v>18</v>
-      </c>
-      <c r="G58" s="6"/>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+        <v>14</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>54</v>
       </c>
@@ -2472,19 +2584,19 @@
         <v>7</v>
       </c>
       <c r="C59" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D59">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="E59">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F59" t="s">
-        <v>18</v>
-      </c>
-      <c r="G59" s="6" t="s">
-        <v>56</v>
+        <v>8</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.2">
@@ -2495,7 +2607,7 @@
         <v>7</v>
       </c>
       <c r="C60" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D60">
         <v>300</v>
@@ -2506,7 +2618,9 @@
       <c r="F60" t="s">
         <v>18</v>
       </c>
-      <c r="G60" s="6"/>
+      <c r="G60" s="8" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
@@ -2516,7 +2630,7 @@
         <v>7</v>
       </c>
       <c r="C61" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D61">
         <v>300</v>
@@ -2525,11 +2639,9 @@
         <v>3</v>
       </c>
       <c r="F61" t="s">
-        <v>22</v>
-      </c>
-      <c r="G61" s="5" t="s">
-        <v>0</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
@@ -2539,20 +2651,22 @@
         <v>7</v>
       </c>
       <c r="C62" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="D62">
         <v>300</v>
       </c>
       <c r="E62">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F62" t="s">
         <v>18</v>
       </c>
-      <c r="G62" s="5"/>
-    </row>
-    <row r="63" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="G62" s="8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>54</v>
       </c>
@@ -2560,22 +2674,20 @@
         <v>7</v>
       </c>
       <c r="C63" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D63">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="E63">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F63" t="s">
-        <v>8</v>
-      </c>
-      <c r="G63" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="68" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+      <c r="G63" s="8"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>54</v>
       </c>
@@ -2583,273 +2695,440 @@
         <v>7</v>
       </c>
       <c r="C64" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D64">
+        <v>300</v>
+      </c>
+      <c r="E64">
+        <v>3</v>
+      </c>
+      <c r="F64" t="s">
+        <v>22</v>
+      </c>
+      <c r="G64" s="7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>54</v>
+      </c>
+      <c r="B65" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" t="s">
+        <v>32</v>
+      </c>
+      <c r="D65">
+        <v>300</v>
+      </c>
+      <c r="E65">
+        <v>1</v>
+      </c>
+      <c r="F65" t="s">
+        <v>18</v>
+      </c>
+      <c r="G65" s="7"/>
+    </row>
+    <row r="66" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>54</v>
+      </c>
+      <c r="B66" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66" t="s">
+        <v>23</v>
+      </c>
+      <c r="D66">
         <v>60</v>
       </c>
-      <c r="E64">
+      <c r="E66">
         <v>1</v>
       </c>
-      <c r="F64" t="s">
-        <v>33</v>
-      </c>
-      <c r="G64" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="68" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
-        <v>103</v>
-      </c>
-      <c r="B65" t="s">
-        <v>104</v>
-      </c>
-      <c r="C65" t="s">
-        <v>105</v>
-      </c>
-      <c r="G65" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" ht="85" x14ac:dyDescent="0.2">
-      <c r="A66" t="s">
-        <v>103</v>
-      </c>
-      <c r="B66" t="s">
-        <v>104</v>
-      </c>
-      <c r="C66" t="s">
-        <v>106</v>
+      <c r="F66" t="s">
+        <v>8</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>115</v>
+        <v>30</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>103</v>
+        <v>54</v>
       </c>
       <c r="B67" t="s">
-        <v>104</v>
+        <v>7</v>
       </c>
       <c r="C67" t="s">
-        <v>107</v>
+        <v>24</v>
       </c>
       <c r="D67">
         <v>60</v>
       </c>
       <c r="E67">
+        <v>1</v>
+      </c>
+      <c r="F67" t="s">
+        <v>33</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="68" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>97</v>
+      </c>
+      <c r="B68" t="s">
+        <v>98</v>
+      </c>
+      <c r="C68" t="s">
+        <v>99</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="85" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>97</v>
+      </c>
+      <c r="B69" t="s">
+        <v>98</v>
+      </c>
+      <c r="C69" t="s">
+        <v>100</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="68" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>97</v>
+      </c>
+      <c r="B70" t="s">
+        <v>98</v>
+      </c>
+      <c r="C70" t="s">
+        <v>101</v>
+      </c>
+      <c r="D70">
+        <v>60</v>
+      </c>
+      <c r="E70">
         <v>3</v>
       </c>
-      <c r="F67" t="s">
-        <v>158</v>
-      </c>
-      <c r="G67" s="1" t="s">
+      <c r="F70" t="s">
+        <v>147</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>97</v>
+      </c>
+      <c r="B71" t="s">
+        <v>98</v>
+      </c>
+      <c r="C71" t="s">
+        <v>102</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="51" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>97</v>
+      </c>
+      <c r="B72" t="s">
+        <v>98</v>
+      </c>
+      <c r="C72" t="s">
+        <v>103</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="51" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>97</v>
+      </c>
+      <c r="B73" t="s">
+        <v>98</v>
+      </c>
+      <c r="C73" t="s">
+        <v>104</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="221" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>113</v>
+      </c>
+      <c r="B74" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
-        <v>103</v>
-      </c>
-      <c r="B68" t="s">
-        <v>104</v>
-      </c>
-      <c r="C68" t="s">
-        <v>108</v>
-      </c>
-      <c r="G68" s="1" t="s">
+      <c r="C74" t="s">
+        <v>111</v>
+      </c>
+      <c r="D74">
+        <v>300</v>
+      </c>
+      <c r="E74">
+        <v>3</v>
+      </c>
+      <c r="F74">
+        <v>60</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="204" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" ht="51" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
-        <v>103</v>
-      </c>
-      <c r="B69" t="s">
-        <v>104</v>
-      </c>
-      <c r="C69" t="s">
-        <v>109</v>
-      </c>
-      <c r="G69" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" ht="51" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
-        <v>103</v>
-      </c>
-      <c r="B70" t="s">
-        <v>104</v>
-      </c>
-      <c r="C70" t="s">
-        <v>110</v>
-      </c>
-      <c r="G70" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" ht="221" x14ac:dyDescent="0.2">
-      <c r="A71" t="s">
-        <v>119</v>
-      </c>
-      <c r="B71" t="s">
-        <v>120</v>
-      </c>
-      <c r="C71" t="s">
-        <v>117</v>
-      </c>
-      <c r="D71">
+      <c r="B75" t="s">
+        <v>114</v>
+      </c>
+      <c r="C75" t="s">
+        <v>294</v>
+      </c>
+      <c r="D75">
         <v>300</v>
-      </c>
-      <c r="E71">
-        <v>3</v>
-      </c>
-      <c r="F71">
-        <v>60</v>
-      </c>
-      <c r="G71" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A72" t="s">
-        <v>119</v>
-      </c>
-      <c r="B72" t="s">
-        <v>120</v>
-      </c>
-      <c r="C72" t="s">
-        <v>125</v>
-      </c>
-      <c r="D72">
-        <v>300</v>
-      </c>
-      <c r="E72">
-        <v>3</v>
-      </c>
-      <c r="F72">
-        <v>60</v>
-      </c>
-      <c r="G72" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A73" t="s">
-        <v>119</v>
-      </c>
-      <c r="B73" t="s">
-        <v>120</v>
-      </c>
-      <c r="C73" t="s">
-        <v>121</v>
-      </c>
-      <c r="D73">
-        <v>60</v>
-      </c>
-      <c r="E73">
-        <v>1</v>
-      </c>
-      <c r="F73">
-        <v>85</v>
-      </c>
-      <c r="G73" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A74" t="s">
-        <v>119</v>
-      </c>
-      <c r="B74" t="s">
-        <v>120</v>
-      </c>
-      <c r="C74" t="s">
-        <v>122</v>
-      </c>
-      <c r="G74" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A75" t="s">
-        <v>119</v>
-      </c>
-      <c r="B75" t="s">
-        <v>120</v>
-      </c>
-      <c r="C75" t="s">
-        <v>147</v>
-      </c>
-      <c r="D75">
-        <v>60</v>
       </c>
       <c r="E75">
         <v>3</v>
       </c>
-      <c r="F75" t="s">
-        <v>130</v>
-      </c>
-      <c r="G75" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="F75">
+        <v>60</v>
+      </c>
+      <c r="G75" s="5" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="153" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B76" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="C76" t="s">
-        <v>148</v>
+        <v>115</v>
       </c>
       <c r="D76">
         <v>60</v>
       </c>
       <c r="E76">
+        <v>1</v>
+      </c>
+      <c r="F76">
+        <v>85</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>113</v>
+      </c>
+      <c r="B77" t="s">
+        <v>114</v>
+      </c>
+      <c r="C77" t="s">
+        <v>116</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>113</v>
+      </c>
+      <c r="B78" t="s">
+        <v>114</v>
+      </c>
+      <c r="C78" t="s">
+        <v>137</v>
+      </c>
+      <c r="D78">
+        <v>60</v>
+      </c>
+      <c r="E78">
         <v>3</v>
       </c>
-      <c r="F76" t="s">
-        <v>130</v>
-      </c>
-      <c r="G76" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="G77" s="3"/>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A78" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="G78" s="3"/>
-    </row>
-    <row r="79" spans="1:7" ht="68" x14ac:dyDescent="0.2">
+      <c r="F78" t="s">
+        <v>123</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
+        <v>113</v>
+      </c>
+      <c r="B79" t="s">
+        <v>114</v>
+      </c>
+      <c r="C79" t="s">
+        <v>321</v>
+      </c>
+      <c r="D79">
+        <v>60</v>
+      </c>
+      <c r="E79">
+        <v>3</v>
+      </c>
+      <c r="F79" t="s">
         <v>123</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" ht="119" x14ac:dyDescent="0.2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>152</v>
+        <v>290</v>
+      </c>
+      <c r="B80" t="s">
+        <v>114</v>
+      </c>
+      <c r="C80" t="s">
+        <v>288</v>
+      </c>
+      <c r="D80">
+        <v>60</v>
+      </c>
+      <c r="E80">
+        <v>3</v>
+      </c>
+      <c r="F80" t="s">
+        <v>64</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>153</v>
+        <v>291</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>290</v>
+      </c>
+      <c r="B81" t="s">
+        <v>114</v>
+      </c>
+      <c r="C81" t="s">
+        <v>289</v>
+      </c>
+      <c r="D81">
+        <v>60</v>
+      </c>
+      <c r="E81">
+        <v>3</v>
+      </c>
+      <c r="F81" t="s">
+        <v>64</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A82" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="G82" s="3"/>
+    </row>
+    <row r="83" spans="1:7" ht="68" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>117</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="119" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>141</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A85" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="D85" s="6">
+        <v>300</v>
+      </c>
+      <c r="E85" s="6">
+        <v>3</v>
+      </c>
+      <c r="F85" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="G85" s="6" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A86" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="D86" s="6"/>
+      <c r="E86" s="6"/>
+      <c r="F86" s="6"/>
+      <c r="G86" s="6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A87" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="D87" s="6"/>
+      <c r="E87" s="6"/>
+      <c r="F87" s="6"/>
+      <c r="G87" s="6" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="G61:G62"/>
-    <mergeCell ref="G59:G60"/>
-    <mergeCell ref="G57:G58"/>
+    <mergeCell ref="G64:G65"/>
+    <mergeCell ref="G62:G63"/>
+    <mergeCell ref="G60:G61"/>
     <mergeCell ref="D1:G1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -2872,10 +3151,10 @@
         <v>50</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -2905,10 +3184,10 @@
         <v>53</v>
       </c>
       <c r="B4" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="C4" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -2916,10 +3195,10 @@
         <v>53</v>
       </c>
       <c r="B5" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="C5" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -2927,10 +3206,10 @@
         <v>53</v>
       </c>
       <c r="B6" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="C6" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -2938,10 +3217,10 @@
         <v>53</v>
       </c>
       <c r="B7" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="C7" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -2949,10 +3228,10 @@
         <v>53</v>
       </c>
       <c r="B8" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="C8" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -2960,10 +3239,10 @@
         <v>53</v>
       </c>
       <c r="B9" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="C9" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -2971,10 +3250,10 @@
         <v>53</v>
       </c>
       <c r="B10" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="C10" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -2982,10 +3261,10 @@
         <v>53</v>
       </c>
       <c r="B11" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="C11" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -2993,10 +3272,10 @@
         <v>53</v>
       </c>
       <c r="B12" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="C12" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -3004,10 +3283,10 @@
         <v>53</v>
       </c>
       <c r="B13" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="C13" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -3015,10 +3294,10 @@
         <v>53</v>
       </c>
       <c r="B14" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="C14" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -3026,10 +3305,10 @@
         <v>53</v>
       </c>
       <c r="B15" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="C15" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -3037,10 +3316,10 @@
         <v>53</v>
       </c>
       <c r="B16" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="C16" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -3048,10 +3327,10 @@
         <v>53</v>
       </c>
       <c r="B17" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="C17" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -3059,10 +3338,10 @@
         <v>53</v>
       </c>
       <c r="B18" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="C18" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -3070,10 +3349,10 @@
         <v>53</v>
       </c>
       <c r="B19" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="C19" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -3081,10 +3360,10 @@
         <v>53</v>
       </c>
       <c r="B20" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="C20" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -3092,10 +3371,10 @@
         <v>53</v>
       </c>
       <c r="B21" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="C21" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -3103,10 +3382,10 @@
         <v>53</v>
       </c>
       <c r="B22" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="C22" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -3114,10 +3393,10 @@
         <v>53</v>
       </c>
       <c r="B23" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="C23" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -3125,10 +3404,10 @@
         <v>53</v>
       </c>
       <c r="B24" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="C24" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -3136,10 +3415,10 @@
         <v>53</v>
       </c>
       <c r="B25" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="C25" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -3147,10 +3426,10 @@
         <v>53</v>
       </c>
       <c r="B26" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="C26" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -3158,10 +3437,10 @@
         <v>53</v>
       </c>
       <c r="B27" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="C27" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -3169,10 +3448,10 @@
         <v>53</v>
       </c>
       <c r="B28" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="C28" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -3180,10 +3459,10 @@
         <v>53</v>
       </c>
       <c r="B29" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="C29" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -3191,10 +3470,10 @@
         <v>53</v>
       </c>
       <c r="B30" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="C30" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
@@ -3202,10 +3481,10 @@
         <v>53</v>
       </c>
       <c r="B31" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="C31" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -3213,10 +3492,10 @@
         <v>53</v>
       </c>
       <c r="B32" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="C32" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -3224,10 +3503,10 @@
         <v>53</v>
       </c>
       <c r="B33" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="C33" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -3235,10 +3514,10 @@
         <v>53</v>
       </c>
       <c r="B34" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="C34" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -3246,10 +3525,10 @@
         <v>53</v>
       </c>
       <c r="B35" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="C35" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
@@ -3257,10 +3536,10 @@
         <v>53</v>
       </c>
       <c r="B36" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="C36" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
@@ -3268,10 +3547,10 @@
         <v>53</v>
       </c>
       <c r="B37" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="C37" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
@@ -3279,10 +3558,10 @@
         <v>53</v>
       </c>
       <c r="B38" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="C38" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
@@ -3290,10 +3569,10 @@
         <v>53</v>
       </c>
       <c r="B39" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="C39" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
@@ -3301,10 +3580,10 @@
         <v>53</v>
       </c>
       <c r="B40" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="C40" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
@@ -3312,10 +3591,10 @@
         <v>53</v>
       </c>
       <c r="B41" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="C41" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
@@ -3323,10 +3602,10 @@
         <v>53</v>
       </c>
       <c r="B42" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="C42" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
@@ -3334,10 +3613,10 @@
         <v>53</v>
       </c>
       <c r="B43" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="C43" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
@@ -3345,10 +3624,10 @@
         <v>53</v>
       </c>
       <c r="B44" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
@@ -3356,10 +3635,10 @@
         <v>53</v>
       </c>
       <c r="B45" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="C45" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
@@ -3367,10 +3646,10 @@
         <v>53</v>
       </c>
       <c r="B46" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="C46" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
@@ -3378,10 +3657,10 @@
         <v>53</v>
       </c>
       <c r="B47" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="C47" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
@@ -3389,10 +3668,10 @@
         <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="C48" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
@@ -3400,10 +3679,10 @@
         <v>53</v>
       </c>
       <c r="B49" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="C49" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
@@ -3411,10 +3690,10 @@
         <v>53</v>
       </c>
       <c r="B50" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="C50" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
@@ -3422,10 +3701,10 @@
         <v>53</v>
       </c>
       <c r="B51" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="C51" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
@@ -3433,10 +3712,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="C52" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
@@ -3444,10 +3723,10 @@
         <v>53</v>
       </c>
       <c r="B53" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="C53" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
@@ -3455,186 +3734,186 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="C54" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="B55" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="C55" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B56" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="C56" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B57" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="C57" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B58" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="C58" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B59" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="C59" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B60" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="C60" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B61" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="C61" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B62" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="C62" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B63" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="C63" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B64" t="s">
+        <v>166</v>
+      </c>
+      <c r="C64" t="s">
         <v>177</v>
-      </c>
-      <c r="C64" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B65" t="s">
+        <v>167</v>
+      </c>
+      <c r="C65" t="s">
         <v>178</v>
-      </c>
-      <c r="C65" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B66" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="C66" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B67" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="C67" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B68" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="C68" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B69" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="C69" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B70" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="C70" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>
